--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,168 +505,178 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>2960358.323387762</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>55456.33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>3015814.653387762</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>3291039.781244973</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3291039.781244973</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>4709026.177726324</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>8000065.958971297</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>3291039.781244973</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>3291039.781244973</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-4934411.090697014</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>8225450.871941987</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>2893733.700012341</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>2893733.700012341</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>-3291039.781244973</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" s="4" t="n">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="4" t="n">
         <v>-397306.081232632</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2026-06-30 (30 days)</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>avalanche_c=89166730, base=48037326, ethereum=25433938, monad=84784216, plume=78267500</t>
+          <t>2026-06-01 → 2026-06-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-03T06:36:22+00:00</t>
+          <t>avalanche_c=89166730, base=48037326, ethereum=25433938, monad=84784216, plume=78267500</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-07T14:51:44+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2893733.700012341</v>
+        <v>2943329.700012341</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>3015814.653387762</v>
+        <v>3065410.653387762</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2893733.700012341</v>
+        <v>2943329.700012341</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>-397306.081232632</v>
+        <v>-347710.081232632</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:44+00:00</t>
+          <t>2026-07-08T18:39:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>782055.9689570594</v>
+        <v>782091.5499017021</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>782055.9689570594</v>
+        <v>782091.5499017021</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-8986.801160020979</v>
+        <v>-9022.382104663577</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>575562.0483953619</v>
+        <v>575588.2345536361</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>575562.0483953619</v>
+        <v>575588.2345536361</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-287129.0676622425</v>
+        <v>-287155.2538205166</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>437270.8242774927</v>
+        <v>437290.7186451723</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>437270.8242774927</v>
+        <v>437290.7186451723</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>77122.49646046347</v>
+        <v>77102.6020927839</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>390424.2794565052</v>
+        <v>390442.0424622566</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>390424.2794565052</v>
+        <v>390442.0424622566</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4486.463254284972</v>
+        <v>-4504.226260036329</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>307805.295322295</v>
+        <v>307819.2994391464</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>307805.295322295</v>
+        <v>307819.2994391464</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-208005.495322295</v>
+        <v>-208019.4994391464</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>302719.7049775741</v>
+        <v>302733.4777169848</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>302719.7049775741</v>
+        <v>302733.4777169848</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>93309.08413497066</v>
+        <v>93295.31139555995</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>139799.4995499541</v>
+        <v>139805.8599620627</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>139799.4995499541</v>
+        <v>139805.8599620627</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231939.1904500459</v>
+        <v>231932.8300379373</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>98837.15746900917</v>
+        <v>98841.65423083713</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>98837.15746900917</v>
+        <v>98841.65423083713</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98837.15746900917</v>
+        <v>-98841.65423083713</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>75642.45658180301</v>
+        <v>75645.8980619107</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>75642.45658180301</v>
+        <v>75645.8980619107</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-5545.023699274447</v>
+        <v>-5548.465179382139</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>75584.27174506056</v>
+        <v>75587.71057795176</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>75584.27174506056</v>
+        <v>75587.71057795176</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-62853.34724506056</v>
+        <v>-62856.78607795177</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>75476.44776437488</v>
+        <v>75479.88169163371</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>75476.44776437488</v>
+        <v>75479.88169163371</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-75142.52043756651</v>
+        <v>-75145.95436482533</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17204.59814940382</v>
+        <v>17205.38090137894</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17204.59814940382</v>
+        <v>17205.38090137894</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1431.675298371111</v>
+        <v>1430.892546395995</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>10610.90958301088</v>
+        <v>10611.39234409381</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>10610.90958301088</v>
+        <v>10611.39234409381</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1519.666987105928</v>
+        <v>1519.184226023005</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1846,13 +1846,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1866.196282294363</v>
+        <v>1866.281188016266</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1866.196282294363</v>
+        <v>1866.281188016266</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1866.196282295967</v>
+        <v>-1866.281188017869</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1865,12 +1865,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1884,40 +1884,40 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>49596</v>
+        <v>10068.978846</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>10068.978846</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>49596</v>
+        <v>10068.978846</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>149.7245486001996</v>
+        <v>30.39845758029373</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>149.7245486001996</v>
+        <v>30.39845758029373</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-49745.7245486002</v>
+        <v>-30.39845758029373</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1930,12 +1930,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1945,44 +1945,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>30.39707461453158</v>
+        <v>0.001110606709394735</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>30.39707461453158</v>
+        <v>0.001110606709394735</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-30.39707461453158</v>
+        <v>-0.0004083716924821368</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1995,12 +1995,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2014,40 +2014,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>1e-06</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>1e-06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.000702235016912599</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>1e-06</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.001110556182783302</v>
+        <v>3.01902090025443e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.001110556182783302</v>
+        <v>3.01902090025443e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.0004083211658707041</v>
+        <v>-3.01902090025443e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2100,19 +2100,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.018883551096854e-09</v>
+        <v>0</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.018883551096854e-09</v>
+        <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.018883551096854e-09</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2125,12 +2125,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2190,12 +2190,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>-49596</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-08T18:39:47+00:00</t>
+          <t>2026-07-09T08:08:47+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>782091.5499017021</v>
+        <v>781971.9934722943</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>782091.5499017021</v>
+        <v>781971.9934722943</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-9022.382104663577</v>
+        <v>-8902.825675255857</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>575588.2345536361</v>
+        <v>575500.2457828317</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>575588.2345536361</v>
+        <v>575500.2457828317</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-287155.2538205166</v>
+        <v>-287067.2650497123</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>437290.7186451723</v>
+        <v>437223.871078617</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>437290.7186451723</v>
+        <v>437223.871078617</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>77102.6020927839</v>
+        <v>77169.44965933914</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>390442.0424622566</v>
+        <v>390382.3565386671</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>390442.0424622566</v>
+        <v>390382.3565386671</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4504.226260036329</v>
+        <v>-4444.540336446807</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>307819.2994391464</v>
+        <v>307772.243852945</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>307819.2994391464</v>
+        <v>307772.243852945</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-208019.4994391464</v>
+        <v>-207972.4438529451</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>302733.4777169848</v>
+        <v>302687.1995879569</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>302733.4777169848</v>
+        <v>302687.1995879569</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>93295.31139555995</v>
+        <v>93341.58952458791</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>139805.8599620627</v>
+        <v>139784.4881809337</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>139805.8599620627</v>
+        <v>139784.4881809337</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231932.8300379373</v>
+        <v>231954.2018190663</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>98841.65423083713</v>
+        <v>98826.54454801536</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>98841.65423083713</v>
+        <v>98826.54454801536</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98841.65423083713</v>
+        <v>-98826.54454801536</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>75645.8980619107</v>
+        <v>75634.33425781033</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>75645.8980619107</v>
+        <v>75634.33425781033</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-5548.465179382139</v>
+        <v>-5536.901375281763</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>75587.71057795176</v>
+        <v>75576.15566883027</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>75587.71057795176</v>
+        <v>75576.15566883027</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-62856.78607795177</v>
+        <v>-62845.23116883027</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>75479.88169163371</v>
+        <v>75468.34326605131</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>75479.88169163371</v>
+        <v>75468.34326605131</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-75145.95436482533</v>
+        <v>-75134.41593924291</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17205.38090137894</v>
+        <v>17202.75075672716</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17205.38090137894</v>
+        <v>17202.75075672716</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1430.892546395995</v>
+        <v>1433.522691047766</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>10611.39234409381</v>
+        <v>10609.77020640434</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>10611.39234409381</v>
+        <v>10609.77020640434</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1519.184226023005</v>
+        <v>1520.806363712465</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1846,13 +1846,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1866.281188016266</v>
+        <v>1865.995894158867</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1866.281188016266</v>
+        <v>1865.995894158867</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1866.281188017869</v>
+        <v>-1865.995894160471</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1865,17 +1865,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1905,19 +1905,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>10068.978846</v>
+        <v>166666.6666666667</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>30.39845758029373</v>
+        <v>503.0932316477092</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>30.39845758029373</v>
+        <v>503.0932316477092</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-30.39845758029373</v>
+        <v>-503.0932316477092</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1930,12 +1930,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1945,44 +1945,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>10068.978846</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>10068.978846</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.000702235016912599</v>
+        <v>0</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>10068.978846</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.001110606709394735</v>
+        <v>30.39381064215937</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.001110606709394735</v>
+        <v>30.39381064215937</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0004083716924821368</v>
+        <v>-30.39381064215937</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1995,12 +1995,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2014,40 +2014,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.01902090025443e-09</v>
+        <v>0.001110436933653432</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.01902090025443e-09</v>
+        <v>0.001110436933653432</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.01902090025443e-09</v>
+        <v>-0.0004082019167408337</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2100,19 +2100,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>3.018559389886255e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0</v>
+        <v>3.018559389886255e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>-3.018559389886255e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2125,12 +2125,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2190,12 +2190,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -2255,12 +2255,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>-49596</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2413,13 +2413,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0</v>
+        <v>1.20325e-09</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0</v>
+        <v>1.20325e-09</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>0</v>
+        <v>1.20325e-09</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
@@ -2445,21 +2445,17 @@
       <c r="R26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2469,7 +2465,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -2482,22 +2478,22 @@
         <v>0</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0</v>
+        <v>-1.20325e-09</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>0</v>
+        <v>-1.20325e-09</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0</v>
+        <v>6.073166666666666e-10</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -2506,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>0</v>
+        <v>-1.20325e-09</v>
       </c>
       <c r="Q27" s="5" t="n">
         <v>0</v>
@@ -2514,17 +2510,21 @@
       <c r="R27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2584,12 +2584,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -2649,17 +2649,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2943329.700012341</v>
+        <v>2943329.700012343</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>3065410.653387762</v>
+        <v>3065410.653387764</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2943329.700012341</v>
+        <v>2943329.700012343</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>-347710.081232632</v>
+        <v>-347710.0812326304</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-09T08:08:47+00:00</t>
+          <t>2026-07-10T11:17:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>781971.9934722943</v>
+        <v>782091.5499017021</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>781971.9934722943</v>
+        <v>782091.5499017021</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-8902.825675255857</v>
+        <v>-9022.382104663582</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>575500.2457828317</v>
+        <v>575588.2345536361</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>575500.2457828317</v>
+        <v>575588.2345536361</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-287067.2650497123</v>
+        <v>-287155.2538205166</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>437223.871078617</v>
+        <v>437290.7186451723</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>437223.871078617</v>
+        <v>437290.7186451723</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>77169.44965933914</v>
+        <v>77102.6020927839</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>390382.3565386671</v>
+        <v>390442.0424622566</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>390382.3565386671</v>
+        <v>390442.0424622566</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4444.540336446807</v>
+        <v>-4504.226260036332</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>307772.243852945</v>
+        <v>307819.2994391464</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>307772.243852945</v>
+        <v>307819.2994391464</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-207972.4438529451</v>
+        <v>-208019.4994391464</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>302687.1995879569</v>
+        <v>302733.4777169848</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>302687.1995879569</v>
+        <v>302733.4777169848</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>93341.58952458791</v>
+        <v>93295.31139555995</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>139784.4881809337</v>
+        <v>139805.8599620627</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>139784.4881809337</v>
+        <v>139805.8599620627</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231954.2018190663</v>
+        <v>231932.8300379373</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>98826.54454801536</v>
+        <v>98841.65423083713</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>98826.54454801536</v>
+        <v>98841.65423083713</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98826.54454801536</v>
+        <v>-98841.65423083713</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>75634.33425781033</v>
+        <v>75645.8980619107</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>75634.33425781033</v>
+        <v>75645.8980619107</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-5536.901375281763</v>
+        <v>-5548.465179382139</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>75576.15566883027</v>
+        <v>75587.71057795176</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>75576.15566883027</v>
+        <v>75587.71057795176</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-62845.23116883027</v>
+        <v>-62856.78607795177</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>75468.34326605131</v>
+        <v>75479.88169163371</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>75468.34326605131</v>
+        <v>75479.88169163371</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-75134.41593924291</v>
+        <v>-75145.95436482533</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17202.75075672716</v>
+        <v>17205.38090137894</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17202.75075672716</v>
+        <v>17205.38090137894</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1433.522691047766</v>
+        <v>1430.892546395995</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>10609.77020640434</v>
+        <v>10611.39234409381</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>10609.77020640434</v>
+        <v>10611.39234409381</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1520.806363712465</v>
+        <v>1519.184226023005</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1828,31 +1828,31 @@
         <v>7547666.106224</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-1.60325e-09</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-1.60325e-09</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>618174.3186537673</v>
+        <v>618174.3186537611</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1865.995894158867</v>
+        <v>1866.281188016247</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1865.995894158867</v>
+        <v>1866.281188016247</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1865.995894160471</v>
+        <v>-1866.281188016247</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1865,17 +1865,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1884,10 +1884,10 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>10068.978846</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>10068.978846</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1905,19 +1905,19 @@
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>166666.6666666667</v>
+        <v>10068.978846</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>503.0932316477092</v>
+        <v>30.39845758029373</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>503.0932316477092</v>
+        <v>30.39845758029373</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-503.0932316477092</v>
+        <v>-30.39845758029373</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1930,12 +1930,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1945,44 +1945,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>30.39381064215937</v>
+        <v>0.001110606709394735</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>30.39381064215937</v>
+        <v>0.001110606709394735</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-30.39381064215937</v>
+        <v>-0.0004083716924821368</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1995,12 +1995,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2014,40 +2014,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>1e-06</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>1e-06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.000702235016912599</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>1e-06</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.001110436933653432</v>
+        <v>3.01902090025443e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.001110436933653432</v>
+        <v>3.01902090025443e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.0004082019167408337</v>
+        <v>-3.01902090025443e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2100,19 +2100,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.018559389886255e-09</v>
+        <v>0</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.018559389886255e-09</v>
+        <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.018559389886255e-09</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2125,12 +2125,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2190,12 +2190,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>-49596</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -2255,12 +2255,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2385,12 +2385,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2413,13 +2413,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>1.20325e-09</v>
+        <v>0</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1.20325e-09</v>
+        <v>0</v>
       </c>
       <c r="K26" s="5" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="5" t="n">
-        <v>1.20325e-09</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>0</v>
@@ -2445,17 +2445,21 @@
       <c r="R26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2465,7 +2469,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -2478,22 +2482,22 @@
         <v>0</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>-1.20325e-09</v>
+        <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-1.20325e-09</v>
+        <v>0</v>
       </c>
       <c r="K27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>6.073166666666666e-10</v>
+        <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -2502,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="5" t="n">
-        <v>-1.20325e-09</v>
+        <v>0</v>
       </c>
       <c r="Q27" s="5" t="n">
         <v>0</v>
@@ -2510,21 +2514,17 @@
       <c r="R27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2584,12 +2584,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -2649,17 +2649,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2893733.700012341</v>
+        <v>2943329.700012343</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>3015814.653387762</v>
+        <v>3065410.653387764</v>
       </c>
     </row>
     <row r="9">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2893733.700012341</v>
+        <v>2943329.700012343</v>
       </c>
     </row>
     <row r="21">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>-397306.081232632</v>
+        <v>-347710.0812326304</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-07T14:51:44+00:00</t>
+          <t>2026-07-10T11:17:39+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>782055.9689570594</v>
+        <v>782091.5499017021</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>782055.9689570594</v>
+        <v>782091.5499017021</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-8986.801160020979</v>
+        <v>-9022.382104663582</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>575562.0483953619</v>
+        <v>575588.2345536361</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>575562.0483953619</v>
+        <v>575588.2345536361</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-287129.0676622425</v>
+        <v>-287155.2538205166</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>437270.8242774927</v>
+        <v>437290.7186451723</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>437270.8242774927</v>
+        <v>437290.7186451723</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>77122.49646046347</v>
+        <v>77102.6020927839</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>390424.2794565052</v>
+        <v>390442.0424622566</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>390424.2794565052</v>
+        <v>390442.0424622566</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4486.463254284972</v>
+        <v>-4504.226260036332</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>307805.295322295</v>
+        <v>307819.2994391464</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>307805.295322295</v>
+        <v>307819.2994391464</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-208005.495322295</v>
+        <v>-208019.4994391464</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>302719.7049775741</v>
+        <v>302733.4777169848</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>302719.7049775741</v>
+        <v>302733.4777169848</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>93309.08413497066</v>
+        <v>93295.31139555995</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>139799.4995499541</v>
+        <v>139805.8599620627</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>139799.4995499541</v>
+        <v>139805.8599620627</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231939.1904500459</v>
+        <v>231932.8300379373</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>98837.15746900917</v>
+        <v>98841.65423083713</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>98837.15746900917</v>
+        <v>98841.65423083713</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98837.15746900917</v>
+        <v>-98841.65423083713</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>75642.45658180301</v>
+        <v>75645.8980619107</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>75642.45658180301</v>
+        <v>75645.8980619107</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-5545.023699274447</v>
+        <v>-5548.465179382139</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>75584.27174506056</v>
+        <v>75587.71057795176</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>75584.27174506056</v>
+        <v>75587.71057795176</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-62853.34724506056</v>
+        <v>-62856.78607795177</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>75476.44776437488</v>
+        <v>75479.88169163371</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>75476.44776437488</v>
+        <v>75479.88169163371</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-75142.52043756651</v>
+        <v>-75145.95436482533</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17204.59814940382</v>
+        <v>17205.38090137894</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17204.59814940382</v>
+        <v>17205.38090137894</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1431.675298371111</v>
+        <v>1430.892546395995</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>10610.90958301088</v>
+        <v>10611.39234409381</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>10610.90958301088</v>
+        <v>10611.39234409381</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1519.666987105928</v>
+        <v>1519.184226023005</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1828,31 +1828,31 @@
         <v>7547666.106224</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-1.60325e-09</v>
+        <v>0</v>
       </c>
       <c r="I17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-1.60325e-09</v>
+        <v>0</v>
       </c>
       <c r="K17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>618174.3186537673</v>
+        <v>618174.3186537611</v>
       </c>
       <c r="M17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1866.196282294363</v>
+        <v>1866.281188016247</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1866.196282294363</v>
+        <v>1866.281188016247</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1866.196282295967</v>
+        <v>-1866.281188016247</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1865,12 +1865,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>AUSD raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1884,40 +1884,40 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>49596</v>
+        <v>10068.978846</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>10068.978846</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="K18" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>49596</v>
+        <v>10068.978846</v>
       </c>
       <c r="M18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>149.7245486001996</v>
+        <v>30.39845758029373</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>149.7245486001996</v>
+        <v>30.39845758029373</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-49745.7245486002</v>
+        <v>-30.39845758029373</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1930,12 +1930,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUSD raw (alt holder idle)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1945,44 +1945,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912598</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>10068.978846</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>30.39707461453158</v>
+        <v>0.001110606709394735</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>30.39707461453158</v>
+        <v>0.001110606709394735</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-30.39707461453158</v>
+        <v>-0.0004083716924821368</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1995,12 +1995,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2014,40 +2014,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>1e-06</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>1e-06</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.000702235016912599</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>1e-06</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.001110556182783302</v>
+        <v>3.01902090025443e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>0.001110556182783302</v>
+        <v>3.01902090025443e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-0.0004083211658707041</v>
+        <v>-3.01902090025443e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2060,12 +2060,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2075,14 +2075,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2100,19 +2100,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>3.018883551096854e-09</v>
+        <v>0</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>3.018883551096854e-09</v>
+        <v>0</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>-3.018883551096854e-09</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2125,12 +2125,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2190,12 +2190,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2205,17 +2205,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>-49596</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-10T11:17:39+00:00</t>
+          <t>2026-07-13T18:40:08+00:00</t>
         </is>
       </c>
     </row>
@@ -1958,13 +1958,13 @@
         <v>0.000702235016912599</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.000702235016912598</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
@@ -1982,7 +1982,7 @@
         <v>0.001110606709394735</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0004083716924821368</v>
+        <v>-0.0004083716924821358</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Off-protocol holdings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3291039.781244973</v>
+        <v>3291457.592906464</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>8000065.958971297</v>
+        <v>8000483.770632788</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>3291039.781244973</v>
+        <v>3291457.592906464</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>8225450.871941987</v>
+        <v>8225868.683603478</v>
       </c>
     </row>
     <row r="19">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-3291039.781244973</v>
+        <v>-3291457.592906464</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" s="4" t="n">
-        <v>-347710.0812326304</v>
+        <v>-348127.8928941209</v>
       </c>
     </row>
     <row r="24">
@@ -666,7 +666,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-13T18:40:08+00:00</t>
+          <t>2026-07-31T00:13:52+00:00</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>782091.5499017021</v>
+        <v>782190.8397892824</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>782091.5499017021</v>
+        <v>782190.8397892824</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-9022.382104663582</v>
+        <v>-9121.67199224389</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1066,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>575588.2345536361</v>
+        <v>575661.3079567543</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>575588.2345536361</v>
+        <v>575661.3079567543</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-287155.2538205166</v>
+        <v>-287228.3272236349</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>437290.7186451723</v>
+        <v>437346.2345835553</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>437290.7186451723</v>
+        <v>437346.2345835553</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>77102.6020927839</v>
+        <v>77047.08615440091</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1196,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>390442.0424622566</v>
+        <v>390491.6107596094</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>390442.0424622566</v>
+        <v>390491.6107596094</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4504.226260036332</v>
+        <v>-4553.794557389213</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1261,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>307819.2994391464</v>
+        <v>307858.3784237489</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>307819.2994391464</v>
+        <v>307858.3784237489</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-208019.4994391464</v>
+        <v>-208058.5784237489</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1326,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>302733.4777169848</v>
+        <v>302771.9110346356</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>302733.4777169848</v>
+        <v>302771.9110346356</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>93295.31139555995</v>
+        <v>93256.87807790923</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>139805.8599620627</v>
+        <v>139823.608917566</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>139805.8599620627</v>
+        <v>139823.608917566</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231932.8300379373</v>
+        <v>231915.081082434</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>98841.65423083713</v>
+        <v>98854.20260415488</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>98841.65423083713</v>
+        <v>98854.20260415488</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98841.65423083713</v>
+        <v>-98854.20260415488</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1521,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>75645.8980619107</v>
+        <v>75655.50163417206</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>75645.8980619107</v>
+        <v>75655.50163417206</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-5548.465179382139</v>
+        <v>-5558.068751643496</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>75587.71057795176</v>
+        <v>75597.30676306166</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>75587.71057795176</v>
+        <v>75597.30676306166</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-62856.78607795177</v>
+        <v>-62866.38226306166</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1651,13 +1651,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>75479.88169163371</v>
+        <v>75489.4641874025</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>75479.88169163371</v>
+        <v>75489.4641874025</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-75145.95436482533</v>
+        <v>-75155.53686059412</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1716,13 +1716,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17205.38090137894</v>
+        <v>17207.56519851869</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17205.38090137894</v>
+        <v>17207.56519851869</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1430.892546395995</v>
+        <v>1428.708249256244</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1781,13 +1781,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>10611.39234409381</v>
+        <v>10612.73950601244</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>10611.39234409381</v>
+        <v>10612.73950601244</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1519.184226023005</v>
+        <v>1517.837064104367</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1846,13 +1846,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1866.281188016247</v>
+        <v>1866.518120443627</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1866.281188016247</v>
+        <v>1866.518120443627</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1866.281188016247</v>
+        <v>-1866.518120443627</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1911,13 +1911,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>30.39845758029373</v>
+        <v>30.40231679528735</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>30.39845758029373</v>
+        <v>30.40231679528735</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-30.39845758029373</v>
+        <v>-30.40231679528735</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1976,13 +1976,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.001110606709394735</v>
+        <v>0.001110747705695405</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.001110606709394735</v>
+        <v>0.001110747705695405</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0004083716924821358</v>
+        <v>-0.0004085126887828062</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -2041,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.01902090025443e-09</v>
+        <v>3.019404177948489e-09</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.01902090025443e-09</v>
+        <v>3.019404177948489e-09</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.01902090025443e-09</v>
+        <v>-3.019404177948489e-09</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.03809333333333333</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="10">
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>0.0383047231109061</v>
+        <v>0.03831000088868387</v>
       </c>
     </row>
     <row r="11">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.03835293769427627</v>
+        <v>0.03835789868900098</v>
       </c>
     </row>
     <row r="12">
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>-7.550665714063191</v>
+        <v>-7.501055766816042</v>
       </c>
     </row>
     <row r="13">
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>63571.67819359694</v>
+        <v>63153.86653210641</v>
       </c>
     </row>
     <row r="15">
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3291039.781244973</v>
+        <v>3291457.592906464</v>
       </c>
     </row>
     <row r="17">
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>63571.67819359694</v>
+        <v>63153.86653210641</v>
       </c>
     </row>
     <row r="19">
@@ -3028,7 +3028,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3089689.117254046</v>
+        <v>3090106.928915537</v>
       </c>
     </row>
     <row r="21">
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3291039.781244973</v>
+        <v>3291457.592906464</v>
       </c>
     </row>
     <row r="25">
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>8000065.958971297</v>
+        <v>8000483.770632788</v>
       </c>
     </row>
     <row r="28">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8225450.871941987</v>
+        <v>8225868.683603478</v>
       </c>
     </row>
     <row r="31">
@@ -3110,7 +3110,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3291039.781244973</v>
+        <v>3291457.592906464</v>
       </c>
     </row>
     <row r="32">
@@ -3655,16 +3655,16 @@
         <v>5</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>0.0378</v>
+        <v>0.0377</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.03807250088868387</v>
+        <v>0.03799333422201721</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>110028.0882975477</v>
+        <v>109819.118855353</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>274304.4664056644</v>
+        <v>274095.4969634697</v>
       </c>
     </row>
     <row r="8">
@@ -3998,16 +3998,16 @@
         <v>5</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.038</v>
+        <v>0.0379</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>107710.5315253391</v>
+        <v>107501.593865721</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>272095.1657236742</v>
+        <v>271886.2280640561</v>
       </c>
     </row>
     <row r="15">
@@ -4047,16 +4047,16 @@
         <v>5</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0.038</v>
+        <v>0.0379</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03815166755535054</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>107340.1992567863</v>
+        <v>107131.2615971681</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>271740.7666762185</v>
+        <v>271531.8290166004</v>
       </c>
     </row>
     <row r="16">
@@ -4096,16 +4096,16 @@
         <v>5</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>105223.0590309393</v>
+        <v>104805.1678217469</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>269639.0131632725</v>
+        <v>269221.1219540802</v>
       </c>
     </row>
     <row r="17">
@@ -4145,16 +4145,16 @@
         <v>5</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M17" s="6" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>103554.1824788502</v>
+        <v>103136.2912696579</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>267986.5585998255</v>
+        <v>267568.6673906332</v>
       </c>
     </row>
     <row r="18">
@@ -4194,16 +4194,16 @@
         <v>5</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>105341.2489156891</v>
+        <v>104923.3577064968</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>269773.6250366644</v>
+        <v>269355.7338274721</v>
       </c>
     </row>
     <row r="19">
@@ -4243,16 +4243,16 @@
         <v>5</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>0.038</v>
+        <v>0.0378</v>
       </c>
       <c r="M19" s="6" t="n">
-        <v>0.03823083422201721</v>
+        <v>0.03807250088868387</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>106707.6619270497</v>
+        <v>106289.7707178574</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>271140.038048025</v>
+        <v>270722.1468388327</v>
       </c>
     </row>
     <row r="20">
@@ -4390,16 +4390,16 @@
         <v>5</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>110730.5887198581</v>
+        <v>111566.2440430196</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>275240.598390727</v>
+        <v>276076.2537138885</v>
       </c>
     </row>
     <row r="23">
@@ -4439,16 +4439,16 @@
         <v>5</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>110717.3513832348</v>
+        <v>111553.0067063962</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>275240.598390727</v>
+        <v>276076.2537138885</v>
       </c>
     </row>
     <row r="24">
@@ -4488,16 +4488,16 @@
         <v>5</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>110684.7683754052</v>
+        <v>111520.4236985667</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>275240.598390727</v>
+        <v>276076.2537138885</v>
       </c>
     </row>
     <row r="25">
@@ -4537,16 +4537,16 @@
         <v>5</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M25" s="6" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>110684.7683754052</v>
+        <v>111520.4236985667</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>275240.598390727</v>
+        <v>276076.2537138885</v>
       </c>
     </row>
     <row r="26">
@@ -4586,16 +4586,16 @@
         <v>5</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>0.0379</v>
+        <v>0.0383</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0.03815166755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>111735.8553072211</v>
+        <v>112571.5106303826</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>276291.6853225429</v>
+        <v>277127.3406457043</v>
       </c>
     </row>
     <row r="27">
@@ -4782,16 +4782,16 @@
         <v>5</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.0385</v>
+        <v>0.0384</v>
       </c>
       <c r="M30" s="6" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.03854750088868387</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>112351.3626937096</v>
+        <v>112142.5044476783</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>276980.5709617764</v>
+        <v>276771.712715745</v>
       </c>
     </row>
     <row r="31">
@@ -4831,16 +4831,16 @@
         <v>5</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="M31" s="6" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>111937.371872578</v>
+        <v>111519.6395025497</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>276582.224502068</v>
+        <v>276164.4921320397</v>
       </c>
     </row>
     <row r="32">
@@ -4880,16 +4880,16 @@
         <v>5</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="M32" s="6" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>111937.371872578</v>
+        <v>111519.6395025497</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>276582.224502068</v>
+        <v>276164.4921320397</v>
       </c>
     </row>
     <row r="33">
@@ -4929,16 +4929,16 @@
         <v>5</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.0385</v>
+        <v>0.0383</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>0.03862666755535054</v>
+        <v>0.0384683342220172</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>111937.371872578</v>
+        <v>111519.6395025497</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>276582.224502068</v>
+        <v>276164.4921320397</v>
       </c>
     </row>
     <row r="34">
@@ -5058,10 +5058,10 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" s="10" t="n">
-        <v>3291039.781244973</v>
+        <v>3291457.592906464</v>
       </c>
       <c r="O37" s="10" t="n">
-        <v>8225450.871941987</v>
+        <v>8225868.683603478</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -2914,7 +2914,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>

--- a/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
+++ b/settlements/grove/2026-06/grove_settlement_june_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2943329.700012343</v>
+        <v>3020509.32487783</v>
       </c>
     </row>
     <row r="5">
@@ -515,168 +515,178 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" s="4" t="n">
-        <v>3065410.653387764</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>+ chronicle_points (20% of base rate on Chronicle Farm USDS)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>15649.89661183517</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" s="4" t="n">
+        <v>3158240.174865086</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>3291457.592906464</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3291457.592906464</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B12" s="3" t="n">
         <v>4709026.177726324</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" s="4" t="n">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" s="4" t="n">
         <v>8000483.770632788</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>3291457.592906464</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3291457.592906464</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B17" s="3" t="n">
         <v>-4934411.090697014</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" s="4" t="n">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" s="4" t="n">
         <v>8225868.683603478</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>2943329.700012343</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3020509.32487783</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B22" s="3" t="n">
         <v>-3291457.592906464</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" s="4" t="n">
-        <v>-348127.8928941209</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-06-01 → 2026-06-30 (30 days)</t>
-        </is>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="4" t="n">
+        <v>-270948.2680286336</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>avalanche_c=89166730, base=48037326, ethereum=25433938, monad=84784216, plume=78267500</t>
+          <t>2026-06-01 → 2026-06-30 (30 days)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-31T00:13:52+00:00</t>
+          <t>avalanche_c=89166730, base=48037326, ethereum=25433938, monad=84784216, plume=78267500</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:22:52+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>
@@ -693,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1001,13 +1011,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>782190.8397892824</v>
+        <v>782179.9785860556</v>
       </c>
       <c r="O4" s="5" t="n">
-        <v>782190.8397892824</v>
+        <v>782179.9785860556</v>
       </c>
       <c r="P4" s="5" t="n">
-        <v>-9121.67199224389</v>
+        <v>-9110.810789017027</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>0</v>
@@ -1066,13 +1076,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>575661.3079567543</v>
+        <v>575653.3145437181</v>
       </c>
       <c r="O5" s="5" t="n">
-        <v>575661.3079567543</v>
+        <v>575653.3145437181</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>-287228.3272236349</v>
+        <v>-287220.3338105987</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>0</v>
@@ -1131,13 +1141,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>437346.2345835553</v>
+        <v>437340.1617607955</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>437346.2345835553</v>
+        <v>437340.1617607955</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>77047.08615440091</v>
+        <v>77053.15897716064</v>
       </c>
       <c r="Q6" s="5" t="n">
         <v>0</v>
@@ -1196,13 +1206,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>390491.6107596094</v>
+        <v>390486.188542259</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>390491.6107596094</v>
+        <v>390486.188542259</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>-4553.794557389213</v>
+        <v>-4548.372340038793</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1261,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>307858.3784237489</v>
+        <v>307854.1036198992</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>307858.3784237489</v>
+        <v>307854.1036198992</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>-208058.5784237489</v>
+        <v>-208054.3036198992</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>0</v>
@@ -1326,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>302771.9110346356</v>
+        <v>302767.7068595291</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>302771.9110346356</v>
+        <v>302767.7068595291</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>93256.87807790923</v>
+        <v>93261.08225301569</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>0</v>
@@ -1391,13 +1401,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>139823.608917566</v>
+        <v>139821.6673803412</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>139823.608917566</v>
+        <v>139821.6673803412</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>231915.081082434</v>
+        <v>231917.0226196588</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>0</v>
@@ -1429,40 +1439,40 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>32754774.88723497</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>32831954.51210045</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>77179.62486548733</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0</v>
+        <v>77179.62486548733</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0</v>
+        <v>77179.62486548733</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>32739638.94138896</v>
+        <v>32754774.88723497</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>98854.20260415488</v>
+        <v>98898.5308559875</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>98854.20260415488</v>
+        <v>98898.5308559875</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>-98854.20260415488</v>
+        <v>-21718.90599050017</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>0</v>
@@ -1521,13 +1531,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>75655.50163417206</v>
+        <v>75654.45111077459</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>75655.50163417206</v>
+        <v>75654.45111077459</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>-5558.068751643496</v>
+        <v>-5557.018228246035</v>
       </c>
       <c r="Q12" s="5" t="n">
         <v>0</v>
@@ -1586,13 +1596,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>75597.30676306166</v>
+        <v>75596.25704773594</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>75597.30676306166</v>
+        <v>75596.25704773594</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>-62866.38226306166</v>
+        <v>-62865.33254773595</v>
       </c>
       <c r="Q13" s="5" t="n">
         <v>0</v>
@@ -1651,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>75489.4641874025</v>
+        <v>75488.4159695376</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>75489.4641874025</v>
+        <v>75488.4159695376</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>-75155.53686059412</v>
+        <v>-75154.48864272921</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>0</v>
@@ -1716,13 +1726,13 @@
         <v>1</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>17207.56519851869</v>
+        <v>17207.32626084114</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>17207.56519851869</v>
+        <v>17207.32626084114</v>
       </c>
       <c r="P15" s="5" t="n">
-        <v>1428.708249256244</v>
+        <v>1428.947186933794</v>
       </c>
       <c r="Q15" s="5" t="n">
         <v>0</v>
@@ -1781,13 +1791,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>10612.73950601244</v>
+        <v>10612.59214156542</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>10612.73950601244</v>
+        <v>10612.59214156542</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>1517.837064104367</v>
+        <v>1517.984428551386</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>0</v>
@@ -1846,13 +1856,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>1866.518120443627</v>
+        <v>1866.492202685963</v>
       </c>
       <c r="O17" s="5" t="n">
-        <v>1866.518120443627</v>
+        <v>1866.492202685963</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>-1866.518120443627</v>
+        <v>-1866.492202685963</v>
       </c>
       <c r="Q17" s="5" t="n">
         <v>0</v>
@@ -1911,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>30.40231679528735</v>
+        <v>30.40189464032915</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>30.40231679528735</v>
+        <v>30.40189464032915</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>-30.40231679528735</v>
+        <v>-30.40189464032915</v>
       </c>
       <c r="Q18" s="5" t="n">
         <v>0</v>
@@ -1930,12 +1940,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E41</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Aave Ethereum RLUSD (aToken)</t>
+          <t>JTRSY Basin escrow — USDS pending subscription (Diamond PAU)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1945,44 +1955,44 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.3685720663589671</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.000702235016912599</v>
+        <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.000702235016912599</v>
+        <v>0</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.000702235016912599</v>
+        <v>0</v>
       </c>
       <c r="K19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.3678698313420545</v>
+        <v>1</v>
       </c>
       <c r="M19" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.001110747705695405</v>
+        <v>0.003019362251655399</v>
       </c>
       <c r="O19" s="5" t="n">
-        <v>0.001110747705695405</v>
+        <v>0.003019362251655399</v>
       </c>
       <c r="P19" s="5" t="n">
-        <v>-0.0004085126887828062</v>
+        <v>-0.003019362251655399</v>
       </c>
       <c r="Q19" s="5" t="n">
         <v>0</v>
@@ -1995,12 +2005,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Aave Horizon RWA USDC (aToken)</t>
+          <t>Aave Ethereum RLUSD (aToken)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2014,40 +2024,40 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3685720663589671</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0</v>
+        <v>0.000702235016912599</v>
       </c>
       <c r="K20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.3678698313420545</v>
       </c>
       <c r="M20" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>3.019404177948489e-09</v>
+        <v>0.001110732282277038</v>
       </c>
       <c r="O20" s="5" t="n">
-        <v>3.019404177948489e-09</v>
+        <v>0.001110732282277038</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>-3.019404177948489e-09</v>
+        <v>-0.0004084972653644387</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>0</v>
@@ -2060,12 +2070,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
+          <t>Aave Horizon RWA USDC (aToken)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2075,14 +2085,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
@@ -2100,19 +2110,19 @@
         <v>0</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="M21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>3.019362251655399e-09</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>0</v>
+        <v>3.019362251655399e-09</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>0</v>
+        <v>-3.019362251655399e-09</v>
       </c>
       <c r="Q21" s="5" t="n">
         <v>0</v>
@@ -2125,12 +2135,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
+          <t>Grove x Steakhouse USDC High Yield (Morpho 4626)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2140,7 +2150,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
@@ -2190,12 +2200,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E13</t>
+          <t>E30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RLUSD raw (ALM idle)</t>
+          <t>Uniswap V3 AUSD/USDC pool (NFT positions — alt holder)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2205,17 +2215,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>49596</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-49596</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
@@ -2255,12 +2265,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (alt holder idle)</t>
+          <t>RLUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2274,13 +2284,13 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>49596</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>-49596</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>0</v>
@@ -2320,12 +2330,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E16</t>
+          <t>E32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (alt holder idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2385,12 +2395,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>E17</t>
+          <t>E16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2428,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="M26" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="5" t="n">
         <v>0</v>
@@ -2445,21 +2455,17 @@
       <c r="R26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E18</t>
+          <t>E17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2469,7 +2475,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
@@ -2497,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="M27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="5" t="n">
         <v>0</v>
@@ -2514,17 +2520,21 @@
       <c r="R27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>E24</t>
+          <t>E18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
+          <t>sUSDS raw / POL (ALM idle — Cat B 4626)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2584,12 +2594,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>E26</t>
+          <t>E24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle)</t>
+          <t>Steakhouse High Yield PYUSD (Morpho 4626)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2599,7 +2609,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -2649,17 +2659,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>E27</t>
+          <t>E26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw on Base (ALM idle)</t>
+          <t>PYUSD raw (ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2714,17 +2724,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>E27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+          <t>USDC raw on Base (ALM idle)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2779,59 +2789,189 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>E38</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Agora AUSD incentives (cash distribution to Grove Eth ALM)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>E40</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>USDS raw (Diamond PAU ALM idle)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
@@ -2924,7 +3064,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (tbill_3m), period avg</t>
+          <t>Reference rate (tbill_3m→sofr@2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
